--- a/260705.xlsx
+++ b/260705.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4F5F4D8-DD82-4777-95DB-DBC71E26EB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CBDB1D-6C2C-4F24-B326-EE24E4E5FBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7240" yWindow="4110" windowWidth="16180" windowHeight="11170" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4110" windowWidth="23470" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -30,18 +30,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>die Briten doch erst mal einen vorlegen.
-Und ich habe ja schon gesagt, damit stärkt man im Nachhinein ja nur die Befürworter des Brexit.
-Die verheerenden Folgen, die sich jetzt abzeichnen für die britische Wirtschaft und auch die Katerstimmung in der Politik, die hat doch manchem gezeigt, also dass man ganz, ganz schnell mit Kritik Dinge kaputtmachen kann nach dem Brexit-Votum.
-Ist doch auch klar, dass es in Europa Defizite gibt.
-Europa muss auch besser werden.
-Wir brauchen ein Europa, das die großen Fragen löst und das uns im Alltag nicht lästig fällt.
-Stichwort Glühbirne.
-Aber es kann doch keinen Zweifel geben, dass.
-Remme: Die Diskussion schwankt ja so ein bisschen, was nötige Folgen angeht, zwischen Pragmatismus einerseits</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
   <si>
     <t>Und das ist mit dem bisher uns zur Verfügung stehenden Ermittlungsinstrumentarium, auch mit den Strafnormen gut fassbar.
 Geuther: 
@@ -66,6 +54,9 @@
 Und ich fand das richtig, dass er nach Marokko geflogen ist, um solche Abkommen zu treffen.
 dass vielleicht auch untaugliche Vorschläge aus den Kreisen der Union gesetzt werden, Vorschläge, die nahe am Populismus sind – Sie haben das Burka-Verbot gerade selbst erwähnt?</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>die Briten doch erst mal einen vorlegen</t>
   </si>
 </sst>
 </file>
@@ -399,9 +390,9 @@
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -420,7 +411,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="196" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -439,7 +430,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +449,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="210" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/260705.xlsx
+++ b/260705.xlsx
@@ -8,16 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CBDB1D-6C2C-4F24-B326-EE24E4E5FBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08ACC86-E651-48A5-972D-091D785CC27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4110" windowWidth="23470" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10320" yWindow="3760" windowWidth="15030" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId2"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,25 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Und das ist mit dem bisher uns zur Verfügung stehenden Ermittlungsinstrumentarium, auch mit den Strafnormen gut fassbar.
-Geuther: 
-ob diese Strafnormen des 129a und b – das heißt also Mitgliedschaft/Unterstützung der terroristischen Vereinigung.
-Das zeigen ja auch eine Reihe von Verurteilungen, die wir in den letzten Jahren erwirkt haben.
-Im Syrien-Irak-Konflikt betätigt sich ja nicht nur der sogenannte Islamische Staat als eine der Konfliktparteien.
-Es gibt dort mehrere, verschiedene Organisationen, unter anderem auch die Jabhat al-Nusra .</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>das sorgfältig zu diskutieren.
-Dabei war für uns immer klar, diese Diskussion  macht erst Sinn, wenn die Verhandlungen soweit fertig sind, dass man auch ein Ergebnis beurteilen kann.
-Und die öffentliche Diskussion in Deutschland, die öffentliche Diskussion in Europa, das, was die Sozialdemokratische Partei als Beitrag in dieser Diskussion geleistet hat, hat ja dazu geführt, dass das ursprünglich verhandelte Abkommen noch einmal verändert worden ist.
-dass der Parteikonvent dem Parteivorsitzenden und Wirtschaftsminister folgt und sagt, dass er in den Gremien der Europäischen Union Ja sagen kann.
-Detjen: Können Sie uns an der Stelle ein Bild Ihrer Partei zeichnen, wie tief spaltet die Diskussion darüber die SPD?
-bei den Freihandelsabkommen, die Regelung mit Ländern betreffen, die so ähnlich sind wie wir in Europa</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>uns niemand daran, das schneller zu tun.
 Im Gegenteil, Herr de Maizière ist ja selbst dafür zuständig, er ist sozusagen der Minister, der das gewährleisten muss.
@@ -57,6 +37,16 @@
   </si>
   <si>
     <t>die Briten doch erst mal einen vorlegen</t>
+  </si>
+  <si>
+    <t>bisher uns zur Verfügung stehenden, den Strafnormen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>betätigt</t>
+  </si>
+  <si>
+    <t>Ländern betreffen, die so ähnlich</t>
   </si>
 </sst>
 </file>
@@ -384,15 +374,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DE0F419-E5C7-4C3F-B246-F9E1BDAC7596}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -402,44 +407,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8656AF48-7B59-4FE9-B40D-402DE6C6AF7C}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="47.08203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="196" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA134D7C-0676-4E9A-A336-18CE94D53124}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39CCFF99-733C-4FA0-8E66-8D808C8939AE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -449,7 +416,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="210" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
